--- a/finviz_stock_data.xlsx
+++ b/finviz_stock_data.xlsx
@@ -518,27 +518,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>32.42B</t>
+          <t>33.11B</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>114.13</t>
+          <t>116.56</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1,082,339</t>
+          <t>369,410</t>
         </is>
       </c>
     </row>
@@ -575,27 +575,27 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7.59B</t>
+          <t>8.06B</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>31.12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-2.78%</t>
+          <t>6.09%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8,075,708</t>
+          <t>3,342,282</t>
         </is>
       </c>
     </row>
@@ -642,17 +642,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>14,745</t>
+          <t>1,645</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>17,111</t>
+          <t>35,740</t>
         </is>
       </c>
     </row>
@@ -756,17 +756,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>33.10</t>
+          <t>33.08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2,738,357</t>
+          <t>2,362,786</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>295.29M</t>
+          <t>295.58M</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>151,602</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>58.75M</t>
+          <t>53.45M</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,17 +870,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.59%</t>
+          <t>-9.02%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>151,926</t>
+          <t>98,723</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>317.16M</t>
+          <t>319.69M</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,17 +927,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>73,715</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -974,27 +974,27 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>705.82M</t>
+          <t>705.20M</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.57</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>88,699</t>
+          <t>15,764</t>
         </is>
       </c>
     </row>
@@ -1041,17 +1041,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>81.97</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2,792</t>
+          <t>322</t>
         </is>
       </c>
     </row>
@@ -1088,27 +1088,27 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.64B</t>
+          <t>8.44B</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>10.49%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>51,215,266</t>
+          <t>80,239,920</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>14.09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>21.36%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2,523</t>
+          <t>25,135</t>
         </is>
       </c>
     </row>
@@ -1202,27 +1202,27 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>461.73M</t>
+          <t>459.98M</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>35.58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2,608</t>
+          <t>9,811</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>45.89M</t>
+          <t>50.17M</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1269,17 +1269,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-6.25%</t>
+          <t>9.33%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>14,725</t>
+          <t>17,622</t>
         </is>
       </c>
     </row>
@@ -1316,27 +1316,27 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.62B</t>
+          <t>1.70B</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>47.38</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>4.49%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>209,218</t>
+          <t>99,629</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.30B</t>
+          <t>1.47B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1383,17 +1383,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>12.97%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>5,699,699</t>
+          <t>3,751,494</t>
         </is>
       </c>
     </row>
@@ -1430,27 +1430,27 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5.86B</t>
+          <t>6.52B</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>54.63</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>72.07</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-10.49%</t>
+          <t>11.18%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>7,087,227</t>
+          <t>1,320,329</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.56B</t>
+          <t>3.60B</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1497,17 +1497,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>59.36</t>
+          <t>60.07</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1,599,808</t>
+          <t>541,675</t>
         </is>
       </c>
     </row>
@@ -1554,17 +1554,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.90</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>517,896</t>
+          <t>442,596</t>
         </is>
       </c>
     </row>
@@ -1611,17 +1611,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1,635,190</t>
+          <t>1,045,091</t>
         </is>
       </c>
     </row>
